--- a/jogos_2025-07-17.xlsx
+++ b/jogos_2025-07-17.xlsx
@@ -717,19 +717,19 @@
         <v>60</v>
       </c>
       <c r="L2">
+        <v>2.56</v>
+      </c>
+      <c r="M2">
+        <v>3.64</v>
+      </c>
+      <c r="N2">
         <v>2.37</v>
-      </c>
-      <c r="M2">
-        <v>3.35</v>
-      </c>
-      <c r="N2">
-        <v>2.65</v>
       </c>
       <c r="O2">
         <v>2.05</v>
       </c>
       <c r="P2">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="Q2">
         <v>1.8</v>
@@ -738,55 +738,55 @@
         <v>1.3</v>
       </c>
       <c r="S2">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="T2">
-        <v>2.5</v>
+        <v>2.45</v>
       </c>
       <c r="U2">
-        <v>1.5</v>
+        <v>1.55</v>
       </c>
       <c r="V2">
         <v>5.5</v>
       </c>
       <c r="W2">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="X2">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y2">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="Z2">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AA2">
-        <v>0</v>
+        <v>4.46</v>
       </c>
       <c r="AB2">
-        <v>1.6</v>
+        <v>1.65</v>
       </c>
       <c r="AC2">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="AD2">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="AE2">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AF2">
-        <v>1.57</v>
+        <v>1.53</v>
       </c>
       <c r="AG2">
-        <v>2.25</v>
+        <v>2.3</v>
       </c>
       <c r="AH2">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="AI2">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AJ2" t="s">
         <v>61</v>
@@ -833,13 +833,13 @@
         <v>60</v>
       </c>
       <c r="L3">
-        <v>2.05</v>
+        <v>1.83</v>
       </c>
       <c r="M3">
-        <v>2.66</v>
+        <v>3.36</v>
       </c>
       <c r="N3">
-        <v>3.91</v>
+        <v>4.74</v>
       </c>
       <c r="O3">
         <v>1.7</v>
@@ -860,19 +860,19 @@
         <v>3.3</v>
       </c>
       <c r="U3">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="V3">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="W3">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="X3">
         <v>1.04</v>
       </c>
       <c r="Y3">
-        <v>6.75</v>
+        <v>6</v>
       </c>
       <c r="Z3">
         <v>1.44</v>
@@ -881,28 +881,28 @@
         <v>2.47</v>
       </c>
       <c r="AB3">
-        <v>2.15</v>
+        <v>2.4</v>
       </c>
       <c r="AC3">
-        <v>1.57</v>
+        <v>1.5</v>
       </c>
       <c r="AD3">
-        <v>4.6</v>
+        <v>4.67</v>
       </c>
       <c r="AE3">
-        <v>1.17</v>
+        <v>1.13</v>
       </c>
       <c r="AF3">
-        <v>2.15</v>
+        <v>2.21</v>
       </c>
       <c r="AG3">
-        <v>1.6</v>
+        <v>1.63</v>
       </c>
       <c r="AH3">
-        <v>11</v>
+        <v>9.5</v>
       </c>
       <c r="AI3">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="AJ3" t="s">
         <v>61</v>
@@ -949,13 +949,13 @@
         <v>60</v>
       </c>
       <c r="L4">
-        <v>2.2</v>
+        <v>2.3</v>
       </c>
       <c r="M4">
-        <v>3.2</v>
+        <v>2.9</v>
       </c>
       <c r="N4">
-        <v>3.45</v>
+        <v>3</v>
       </c>
       <c r="O4">
         <v>1.73</v>
@@ -970,28 +970,28 @@
         <v>1.44</v>
       </c>
       <c r="S4">
-        <v>2.5</v>
+        <v>2.37</v>
       </c>
       <c r="T4">
         <v>3.42</v>
       </c>
       <c r="U4">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="V4">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="W4">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="X4">
-        <v>1.06</v>
+        <v>1.1</v>
       </c>
       <c r="Y4">
         <v>7.3</v>
       </c>
       <c r="Z4">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="AA4">
         <v>2.6</v>
@@ -1000,25 +1000,25 @@
         <v>2.4</v>
       </c>
       <c r="AC4">
-        <v>1.55</v>
+        <v>1.53</v>
       </c>
       <c r="AD4">
-        <v>4.75</v>
+        <v>4.5</v>
       </c>
       <c r="AE4">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="AF4">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="AG4">
         <v>1.67</v>
       </c>
       <c r="AH4">
-        <v>11</v>
+        <v>9.5</v>
       </c>
       <c r="AI4">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="AJ4" t="s">
         <v>61</v>
@@ -1181,13 +1181,13 @@
         <v>60</v>
       </c>
       <c r="L6">
-        <v>2.59</v>
+        <v>2.5</v>
       </c>
       <c r="M6">
-        <v>2.59</v>
+        <v>2.95</v>
       </c>
       <c r="N6">
-        <v>2.88</v>
+        <v>3.05</v>
       </c>
       <c r="O6">
         <v>2</v>
@@ -1199,55 +1199,55 @@
         <v>2.25</v>
       </c>
       <c r="R6">
-        <v>1.57</v>
+        <v>1.62</v>
       </c>
       <c r="S6">
-        <v>2.3</v>
+        <v>2.25</v>
       </c>
       <c r="T6">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="U6">
-        <v>1.23</v>
+        <v>1.25</v>
       </c>
       <c r="V6">
-        <v>13</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="W6">
         <v>1.01</v>
       </c>
       <c r="X6">
-        <v>1.07</v>
+        <v>1.12</v>
       </c>
       <c r="Y6">
         <v>5.75</v>
       </c>
       <c r="Z6">
-        <v>1.48</v>
+        <v>1.53</v>
       </c>
       <c r="AA6">
-        <v>2.37</v>
+        <v>2.4</v>
       </c>
       <c r="AB6">
-        <v>2.63</v>
+        <v>2.65</v>
       </c>
       <c r="AC6">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="AD6">
         <v>5.75</v>
       </c>
       <c r="AE6">
-        <v>1.07</v>
+        <v>1.13</v>
       </c>
       <c r="AF6">
-        <v>2.25</v>
+        <v>2.21</v>
       </c>
       <c r="AG6">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="AH6">
-        <v>11.5</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="AI6">
         <v>1.04</v>

--- a/jogos_2025-07-17.xlsx
+++ b/jogos_2025-07-17.xlsx
@@ -717,13 +717,13 @@
         <v>60</v>
       </c>
       <c r="L2">
-        <v>2.56</v>
+        <v>2.37</v>
       </c>
       <c r="M2">
-        <v>3.64</v>
+        <v>3.35</v>
       </c>
       <c r="N2">
-        <v>2.37</v>
+        <v>2.65</v>
       </c>
       <c r="O2">
         <v>2.05</v>
@@ -741,16 +741,16 @@
         <v>3.3</v>
       </c>
       <c r="T2">
-        <v>2.45</v>
+        <v>2.36</v>
       </c>
       <c r="U2">
-        <v>1.55</v>
+        <v>1.5</v>
       </c>
       <c r="V2">
-        <v>5.5</v>
+        <v>5.75</v>
       </c>
       <c r="W2">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="X2">
         <v>1.01</v>
@@ -762,13 +762,13 @@
         <v>1.2</v>
       </c>
       <c r="AA2">
-        <v>4.46</v>
+        <v>4</v>
       </c>
       <c r="AB2">
-        <v>1.65</v>
+        <v>1.6</v>
       </c>
       <c r="AC2">
-        <v>2.15</v>
+        <v>2.1</v>
       </c>
       <c r="AD2">
         <v>2.6</v>
@@ -777,7 +777,7 @@
         <v>1.44</v>
       </c>
       <c r="AF2">
-        <v>1.53</v>
+        <v>1.55</v>
       </c>
       <c r="AG2">
         <v>2.3</v>
@@ -786,7 +786,7 @@
         <v>4.5</v>
       </c>
       <c r="AI2">
-        <v>1.2</v>
+        <v>1.17</v>
       </c>
       <c r="AJ2" t="s">
         <v>61</v>
@@ -833,13 +833,13 @@
         <v>60</v>
       </c>
       <c r="L3">
-        <v>1.83</v>
+        <v>2.05</v>
       </c>
       <c r="M3">
-        <v>3.36</v>
+        <v>2.66</v>
       </c>
       <c r="N3">
-        <v>4.74</v>
+        <v>3.91</v>
       </c>
       <c r="O3">
         <v>1.7</v>
@@ -863,43 +863,43 @@
         <v>1.28</v>
       </c>
       <c r="V3">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="W3">
         <v>1.03</v>
       </c>
       <c r="X3">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="Y3">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Z3">
         <v>1.44</v>
       </c>
       <c r="AA3">
-        <v>2.47</v>
+        <v>2.5</v>
       </c>
       <c r="AB3">
-        <v>2.4</v>
+        <v>2.15</v>
       </c>
       <c r="AC3">
-        <v>1.5</v>
+        <v>1.57</v>
       </c>
       <c r="AD3">
-        <v>4.67</v>
+        <v>4.79</v>
       </c>
       <c r="AE3">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="AF3">
-        <v>2.21</v>
+        <v>2.06</v>
       </c>
       <c r="AG3">
-        <v>1.63</v>
+        <v>1.65</v>
       </c>
       <c r="AH3">
-        <v>9.5</v>
+        <v>8.9</v>
       </c>
       <c r="AI3">
         <v>1.05</v>
@@ -949,13 +949,13 @@
         <v>60</v>
       </c>
       <c r="L4">
-        <v>2.3</v>
+        <v>2.25</v>
       </c>
       <c r="M4">
-        <v>2.9</v>
+        <v>3.2</v>
       </c>
       <c r="N4">
-        <v>3</v>
+        <v>3.25</v>
       </c>
       <c r="O4">
         <v>1.73</v>
@@ -967,52 +967,52 @@
         <v>2.5</v>
       </c>
       <c r="R4">
-        <v>1.44</v>
+        <v>1.55</v>
       </c>
       <c r="S4">
-        <v>2.37</v>
+        <v>2.55</v>
       </c>
       <c r="T4">
-        <v>3.42</v>
+        <v>3.4</v>
       </c>
       <c r="U4">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="V4">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="W4">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="X4">
-        <v>1.1</v>
+        <v>1.03</v>
       </c>
       <c r="Y4">
-        <v>7.3</v>
+        <v>7</v>
       </c>
       <c r="Z4">
-        <v>1.43</v>
+        <v>1.48</v>
       </c>
       <c r="AA4">
-        <v>2.6</v>
+        <v>2.7</v>
       </c>
       <c r="AB4">
         <v>2.4</v>
       </c>
       <c r="AC4">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="AD4">
         <v>4.5</v>
       </c>
       <c r="AE4">
-        <v>1.18</v>
+        <v>1.14</v>
       </c>
       <c r="AF4">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="AG4">
-        <v>1.67</v>
+        <v>1.65</v>
       </c>
       <c r="AH4">
         <v>9.5</v>
@@ -1181,13 +1181,13 @@
         <v>60</v>
       </c>
       <c r="L6">
-        <v>2.5</v>
+        <v>2.59</v>
       </c>
       <c r="M6">
-        <v>2.95</v>
+        <v>2.59</v>
       </c>
       <c r="N6">
-        <v>3.05</v>
+        <v>2.88</v>
       </c>
       <c r="O6">
         <v>2</v>
@@ -1202,13 +1202,13 @@
         <v>1.62</v>
       </c>
       <c r="S6">
-        <v>2.25</v>
+        <v>1.97</v>
       </c>
       <c r="T6">
         <v>3.75</v>
       </c>
       <c r="U6">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="V6">
         <v>8.800000000000001</v>
@@ -1223,16 +1223,16 @@
         <v>5.75</v>
       </c>
       <c r="Z6">
-        <v>1.53</v>
+        <v>1.48</v>
       </c>
       <c r="AA6">
-        <v>2.4</v>
+        <v>2.37</v>
       </c>
       <c r="AB6">
-        <v>2.65</v>
+        <v>2.75</v>
       </c>
       <c r="AC6">
-        <v>1.42</v>
+        <v>1.4</v>
       </c>
       <c r="AD6">
         <v>5.75</v>
@@ -1241,7 +1241,7 @@
         <v>1.13</v>
       </c>
       <c r="AF6">
-        <v>2.21</v>
+        <v>2.2</v>
       </c>
       <c r="AG6">
         <v>1.62</v>

--- a/jogos_2025-07-17.xlsx
+++ b/jogos_2025-07-17.xlsx
@@ -148,12 +148,12 @@
     <t>Iceland Úrvalsdeild</t>
   </si>
   <si>
+    <t>Brazil Serie A</t>
+  </si>
+  <si>
     <t>Brazil Serie B</t>
   </si>
   <si>
-    <t>Brazil Serie A</t>
-  </si>
-  <si>
     <t>USA MLS Next Pro</t>
   </si>
   <si>
@@ -163,12 +163,12 @@
     <t>Afturelding</t>
   </si>
   <si>
+    <t>Fluminense</t>
+  </si>
+  <si>
     <t>Operário PR</t>
   </si>
   <si>
-    <t>Fluminense</t>
-  </si>
-  <si>
     <t>Houston Dynamo FC II</t>
   </si>
   <si>
@@ -181,10 +181,10 @@
     <t>Fram</t>
   </si>
   <si>
+    <t>Cruzeiro</t>
+  </si>
+  <si>
     <t>CRB</t>
-  </si>
-  <si>
-    <t>Cruzeiro</t>
   </si>
   <si>
     <t>Whitecaps II</t>
@@ -738,31 +738,31 @@
         <v>1.3</v>
       </c>
       <c r="S2">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="T2">
-        <v>2.36</v>
+        <v>2.37</v>
       </c>
       <c r="U2">
         <v>1.5</v>
       </c>
       <c r="V2">
-        <v>5.75</v>
+        <v>5.5</v>
       </c>
       <c r="W2">
         <v>1.13</v>
       </c>
       <c r="X2">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="Y2">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="Z2">
-        <v>1.2</v>
+        <v>1.15</v>
       </c>
       <c r="AA2">
-        <v>4</v>
+        <v>4.3</v>
       </c>
       <c r="AB2">
         <v>1.6</v>
@@ -771,10 +771,10 @@
         <v>2.1</v>
       </c>
       <c r="AD2">
-        <v>2.6</v>
+        <v>2.54</v>
       </c>
       <c r="AE2">
-        <v>1.44</v>
+        <v>1.48</v>
       </c>
       <c r="AF2">
         <v>1.55</v>
@@ -783,7 +783,7 @@
         <v>2.3</v>
       </c>
       <c r="AH2">
-        <v>4.5</v>
+        <v>4.8</v>
       </c>
       <c r="AI2">
         <v>1.17</v>
@@ -833,73 +833,73 @@
         <v>60</v>
       </c>
       <c r="L3">
-        <v>2.05</v>
+        <v>2.43</v>
       </c>
       <c r="M3">
-        <v>2.66</v>
+        <v>3</v>
       </c>
       <c r="N3">
-        <v>3.91</v>
+        <v>2.67</v>
       </c>
       <c r="O3">
-        <v>1.7</v>
+        <v>1.73</v>
       </c>
       <c r="P3">
-        <v>6.25</v>
+        <v>7.25</v>
       </c>
       <c r="Q3">
-        <v>2.88</v>
+        <v>2.5</v>
       </c>
       <c r="R3">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="S3">
-        <v>2.5</v>
+        <v>2.65</v>
       </c>
       <c r="T3">
         <v>3.3</v>
       </c>
       <c r="U3">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="V3">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="W3">
-        <v>1.03</v>
+        <v>1</v>
       </c>
       <c r="X3">
-        <v>1.05</v>
+        <v>1.09</v>
       </c>
       <c r="Y3">
-        <v>7</v>
+        <v>6.5</v>
       </c>
       <c r="Z3">
-        <v>1.44</v>
+        <v>1.48</v>
       </c>
       <c r="AA3">
-        <v>2.5</v>
+        <v>2.6</v>
       </c>
       <c r="AB3">
-        <v>2.15</v>
+        <v>2.43</v>
       </c>
       <c r="AC3">
-        <v>1.57</v>
+        <v>1.49</v>
       </c>
       <c r="AD3">
-        <v>4.79</v>
+        <v>4.6</v>
       </c>
       <c r="AE3">
-        <v>1.12</v>
+        <v>1.18</v>
       </c>
       <c r="AF3">
-        <v>2.06</v>
+        <v>2.05</v>
       </c>
       <c r="AG3">
-        <v>1.65</v>
+        <v>1.72</v>
       </c>
       <c r="AH3">
-        <v>8.9</v>
+        <v>9.5</v>
       </c>
       <c r="AI3">
         <v>1.05</v>
@@ -949,28 +949,28 @@
         <v>60</v>
       </c>
       <c r="L4">
-        <v>2.25</v>
+        <v>2.05</v>
       </c>
       <c r="M4">
-        <v>3.2</v>
+        <v>2.66</v>
       </c>
       <c r="N4">
-        <v>3.25</v>
+        <v>3.91</v>
       </c>
       <c r="O4">
-        <v>1.73</v>
+        <v>1.7</v>
       </c>
       <c r="P4">
-        <v>7.25</v>
+        <v>6.25</v>
       </c>
       <c r="Q4">
-        <v>2.5</v>
+        <v>2.88</v>
       </c>
       <c r="R4">
-        <v>1.55</v>
+        <v>1.6</v>
       </c>
       <c r="S4">
-        <v>2.55</v>
+        <v>2.15</v>
       </c>
       <c r="T4">
         <v>3.4</v>
@@ -979,40 +979,40 @@
         <v>1.3</v>
       </c>
       <c r="V4">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="W4">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="X4">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="Y4">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Z4">
-        <v>1.48</v>
+        <v>1.43</v>
       </c>
       <c r="AA4">
         <v>2.7</v>
       </c>
       <c r="AB4">
-        <v>2.4</v>
+        <v>2.15</v>
       </c>
       <c r="AC4">
-        <v>1.5</v>
+        <v>1.57</v>
       </c>
       <c r="AD4">
-        <v>4.5</v>
+        <v>5</v>
       </c>
       <c r="AE4">
-        <v>1.14</v>
+        <v>1.17</v>
       </c>
       <c r="AF4">
-        <v>2.1</v>
+        <v>2.34</v>
       </c>
       <c r="AG4">
-        <v>1.65</v>
+        <v>1.6</v>
       </c>
       <c r="AH4">
         <v>9.5</v>
@@ -1154,7 +1154,7 @@
         <v>41</v>
       </c>
       <c r="C6" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D6" t="s">
         <v>47</v>
@@ -1199,10 +1199,10 @@
         <v>2.25</v>
       </c>
       <c r="R6">
-        <v>1.62</v>
+        <v>1.6</v>
       </c>
       <c r="S6">
-        <v>1.97</v>
+        <v>2.3</v>
       </c>
       <c r="T6">
         <v>3.75</v>
@@ -1211,16 +1211,16 @@
         <v>1.22</v>
       </c>
       <c r="V6">
-        <v>8.800000000000001</v>
+        <v>12</v>
       </c>
       <c r="W6">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="X6">
-        <v>1.12</v>
+        <v>1.06</v>
       </c>
       <c r="Y6">
-        <v>5.75</v>
+        <v>7</v>
       </c>
       <c r="Z6">
         <v>1.48</v>
@@ -1241,16 +1241,16 @@
         <v>1.13</v>
       </c>
       <c r="AF6">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="AG6">
-        <v>1.62</v>
+        <v>1.57</v>
       </c>
       <c r="AH6">
-        <v>9.300000000000001</v>
+        <v>11.5</v>
       </c>
       <c r="AI6">
-        <v>1.04</v>
+        <v>1</v>
       </c>
       <c r="AJ6" t="s">
         <v>61</v>

--- a/jogos_2025-07-17.xlsx
+++ b/jogos_2025-07-17.xlsx
@@ -717,13 +717,13 @@
         <v>60</v>
       </c>
       <c r="L2">
-        <v>2.37</v>
+        <v>2.58</v>
       </c>
       <c r="M2">
-        <v>3.35</v>
+        <v>3.65</v>
       </c>
       <c r="N2">
-        <v>2.65</v>
+        <v>2.44</v>
       </c>
       <c r="O2">
         <v>2.05</v>
@@ -735,10 +735,10 @@
         <v>1.8</v>
       </c>
       <c r="R2">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="S2">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="T2">
         <v>2.37</v>
@@ -765,10 +765,10 @@
         <v>4.3</v>
       </c>
       <c r="AB2">
-        <v>1.6</v>
+        <v>1.62</v>
       </c>
       <c r="AC2">
-        <v>2.1</v>
+        <v>2.21</v>
       </c>
       <c r="AD2">
         <v>2.54</v>
@@ -780,13 +780,13 @@
         <v>1.55</v>
       </c>
       <c r="AG2">
-        <v>2.3</v>
+        <v>2.35</v>
       </c>
       <c r="AH2">
         <v>4.8</v>
       </c>
       <c r="AI2">
-        <v>1.17</v>
+        <v>1.14</v>
       </c>
       <c r="AJ2" t="s">
         <v>61</v>
@@ -833,13 +833,13 @@
         <v>60</v>
       </c>
       <c r="L3">
-        <v>2.43</v>
+        <v>2.26</v>
       </c>
       <c r="M3">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="N3">
-        <v>2.67</v>
+        <v>3.15</v>
       </c>
       <c r="O3">
         <v>1.73</v>
@@ -854,7 +854,7 @@
         <v>1.44</v>
       </c>
       <c r="S3">
-        <v>2.65</v>
+        <v>2.55</v>
       </c>
       <c r="T3">
         <v>3.3</v>
@@ -866,7 +866,7 @@
         <v>8</v>
       </c>
       <c r="W3">
-        <v>1</v>
+        <v>1.03</v>
       </c>
       <c r="X3">
         <v>1.09</v>
@@ -875,28 +875,28 @@
         <v>6.5</v>
       </c>
       <c r="Z3">
-        <v>1.48</v>
+        <v>1.46</v>
       </c>
       <c r="AA3">
-        <v>2.6</v>
+        <v>2.5</v>
       </c>
       <c r="AB3">
-        <v>2.43</v>
+        <v>2.38</v>
       </c>
       <c r="AC3">
-        <v>1.49</v>
+        <v>1.53</v>
       </c>
       <c r="AD3">
         <v>4.6</v>
       </c>
       <c r="AE3">
-        <v>1.18</v>
+        <v>1.14</v>
       </c>
       <c r="AF3">
-        <v>2.05</v>
+        <v>2.03</v>
       </c>
       <c r="AG3">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="AH3">
         <v>9.5</v>
@@ -949,13 +949,13 @@
         <v>60</v>
       </c>
       <c r="L4">
-        <v>2.05</v>
+        <v>1.85</v>
       </c>
       <c r="M4">
-        <v>2.66</v>
+        <v>2.97</v>
       </c>
       <c r="N4">
-        <v>3.91</v>
+        <v>3.65</v>
       </c>
       <c r="O4">
         <v>1.7</v>
@@ -967,10 +967,10 @@
         <v>2.88</v>
       </c>
       <c r="R4">
-        <v>1.6</v>
+        <v>1.53</v>
       </c>
       <c r="S4">
-        <v>2.15</v>
+        <v>2.5</v>
       </c>
       <c r="T4">
         <v>3.4</v>
@@ -994,28 +994,28 @@
         <v>1.43</v>
       </c>
       <c r="AA4">
-        <v>2.7</v>
+        <v>2.4</v>
       </c>
       <c r="AB4">
-        <v>2.15</v>
+        <v>2.47</v>
       </c>
       <c r="AC4">
-        <v>1.57</v>
+        <v>1.5</v>
       </c>
       <c r="AD4">
         <v>5</v>
       </c>
       <c r="AE4">
-        <v>1.17</v>
+        <v>1.19</v>
       </c>
       <c r="AF4">
-        <v>2.34</v>
+        <v>2.15</v>
       </c>
       <c r="AG4">
         <v>1.6</v>
       </c>
       <c r="AH4">
-        <v>9.5</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="AI4">
         <v>1.05</v>
@@ -1065,13 +1065,13 @@
         <v>60</v>
       </c>
       <c r="L5">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="M5">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="N5">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="O5">
         <v>0</v>
@@ -1083,58 +1083,58 @@
         <v>0</v>
       </c>
       <c r="R5">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="S5">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="T5">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="U5">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="V5">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="W5">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X5">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y5">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="Z5">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AA5">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="AB5">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AC5">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AD5">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="AE5">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AF5">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AG5">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AH5">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="AI5">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AJ5" t="s">
         <v>61</v>
@@ -1181,13 +1181,13 @@
         <v>60</v>
       </c>
       <c r="L6">
-        <v>2.59</v>
+        <v>2.28</v>
       </c>
       <c r="M6">
-        <v>2.59</v>
+        <v>2.81</v>
       </c>
       <c r="N6">
-        <v>2.88</v>
+        <v>3.1</v>
       </c>
       <c r="O6">
         <v>2</v>
@@ -1199,10 +1199,10 @@
         <v>2.25</v>
       </c>
       <c r="R6">
-        <v>1.6</v>
+        <v>1.57</v>
       </c>
       <c r="S6">
-        <v>2.3</v>
+        <v>2.25</v>
       </c>
       <c r="T6">
         <v>3.75</v>
@@ -1217,22 +1217,22 @@
         <v>1.04</v>
       </c>
       <c r="X6">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="Y6">
         <v>7</v>
       </c>
       <c r="Z6">
-        <v>1.48</v>
+        <v>1.57</v>
       </c>
       <c r="AA6">
-        <v>2.37</v>
+        <v>2.4</v>
       </c>
       <c r="AB6">
-        <v>2.75</v>
+        <v>2.65</v>
       </c>
       <c r="AC6">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="AD6">
         <v>5.75</v>
@@ -1244,7 +1244,7 @@
         <v>2.1</v>
       </c>
       <c r="AG6">
-        <v>1.57</v>
+        <v>1.62</v>
       </c>
       <c r="AH6">
         <v>11.5</v>
@@ -1297,40 +1297,40 @@
         <v>60</v>
       </c>
       <c r="L7">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="M7">
-        <v>0</v>
+        <v>3.82</v>
       </c>
       <c r="N7">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="O7">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="P7">
         <v>0</v>
       </c>
       <c r="Q7">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="R7">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="S7">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="T7">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="U7">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="V7">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="W7">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="X7">
         <v>0</v>
@@ -1339,34 +1339,34 @@
         <v>0</v>
       </c>
       <c r="Z7">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AA7">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="AB7">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AC7">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="AD7">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="AE7">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AF7">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AG7">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AH7">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="AI7">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AJ7" t="s">
         <v>61</v>

--- a/jogos_2025-07-17.xlsx
+++ b/jogos_2025-07-17.xlsx
@@ -717,10 +717,10 @@
         <v>60</v>
       </c>
       <c r="L2">
-        <v>2.58</v>
+        <v>2.46</v>
       </c>
       <c r="M2">
-        <v>3.65</v>
+        <v>3.52</v>
       </c>
       <c r="N2">
         <v>2.44</v>
@@ -735,43 +735,43 @@
         <v>1.8</v>
       </c>
       <c r="R2">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="S2">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="T2">
-        <v>2.37</v>
+        <v>2.43</v>
       </c>
       <c r="U2">
-        <v>1.5</v>
+        <v>1.48</v>
       </c>
       <c r="V2">
-        <v>5.5</v>
+        <v>5.75</v>
       </c>
       <c r="W2">
         <v>1.13</v>
       </c>
       <c r="X2">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="Y2">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="Z2">
-        <v>1.15</v>
+        <v>1.18</v>
       </c>
       <c r="AA2">
-        <v>4.3</v>
+        <v>4.35</v>
       </c>
       <c r="AB2">
-        <v>1.62</v>
+        <v>1.6</v>
       </c>
       <c r="AC2">
-        <v>2.21</v>
+        <v>2.1</v>
       </c>
       <c r="AD2">
-        <v>2.54</v>
+        <v>2.55</v>
       </c>
       <c r="AE2">
         <v>1.48</v>
@@ -780,13 +780,13 @@
         <v>1.55</v>
       </c>
       <c r="AG2">
-        <v>2.35</v>
+        <v>2.3</v>
       </c>
       <c r="AH2">
-        <v>4.8</v>
+        <v>4.33</v>
       </c>
       <c r="AI2">
-        <v>1.14</v>
+        <v>1.18</v>
       </c>
       <c r="AJ2" t="s">
         <v>61</v>
@@ -833,13 +833,13 @@
         <v>60</v>
       </c>
       <c r="L3">
-        <v>2.26</v>
+        <v>2.25</v>
       </c>
       <c r="M3">
         <v>3.1</v>
       </c>
       <c r="N3">
-        <v>3.15</v>
+        <v>3.05</v>
       </c>
       <c r="O3">
         <v>1.73</v>
@@ -851,58 +851,58 @@
         <v>2.5</v>
       </c>
       <c r="R3">
-        <v>1.44</v>
+        <v>1.62</v>
       </c>
       <c r="S3">
-        <v>2.55</v>
+        <v>2.5</v>
       </c>
       <c r="T3">
-        <v>3.3</v>
+        <v>3.6</v>
       </c>
       <c r="U3">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="V3">
-        <v>8</v>
+        <v>7.5</v>
       </c>
       <c r="W3">
+        <v>1.04</v>
+      </c>
+      <c r="X3">
+        <v>1.12</v>
+      </c>
+      <c r="Y3">
+        <v>6.05</v>
+      </c>
+      <c r="Z3">
+        <v>1.57</v>
+      </c>
+      <c r="AA3">
+        <v>2.3</v>
+      </c>
+      <c r="AB3">
+        <v>2.87</v>
+      </c>
+      <c r="AC3">
+        <v>1.4</v>
+      </c>
+      <c r="AD3">
+        <v>5.25</v>
+      </c>
+      <c r="AE3">
+        <v>1.11</v>
+      </c>
+      <c r="AF3">
+        <v>2.1</v>
+      </c>
+      <c r="AG3">
+        <v>1.7</v>
+      </c>
+      <c r="AH3">
+        <v>11.5</v>
+      </c>
+      <c r="AI3">
         <v>1.03</v>
-      </c>
-      <c r="X3">
-        <v>1.09</v>
-      </c>
-      <c r="Y3">
-        <v>6.5</v>
-      </c>
-      <c r="Z3">
-        <v>1.46</v>
-      </c>
-      <c r="AA3">
-        <v>2.5</v>
-      </c>
-      <c r="AB3">
-        <v>2.38</v>
-      </c>
-      <c r="AC3">
-        <v>1.53</v>
-      </c>
-      <c r="AD3">
-        <v>4.6</v>
-      </c>
-      <c r="AE3">
-        <v>1.14</v>
-      </c>
-      <c r="AF3">
-        <v>2.03</v>
-      </c>
-      <c r="AG3">
-        <v>1.73</v>
-      </c>
-      <c r="AH3">
-        <v>9.5</v>
-      </c>
-      <c r="AI3">
-        <v>1.05</v>
       </c>
       <c r="AJ3" t="s">
         <v>61</v>
@@ -949,13 +949,13 @@
         <v>60</v>
       </c>
       <c r="L4">
-        <v>1.85</v>
+        <v>2.05</v>
       </c>
       <c r="M4">
-        <v>2.97</v>
+        <v>3</v>
       </c>
       <c r="N4">
-        <v>3.65</v>
+        <v>4.55</v>
       </c>
       <c r="O4">
         <v>1.7</v>
@@ -967,16 +967,16 @@
         <v>2.88</v>
       </c>
       <c r="R4">
-        <v>1.53</v>
+        <v>1.56</v>
       </c>
       <c r="S4">
         <v>2.5</v>
       </c>
       <c r="T4">
-        <v>3.4</v>
+        <v>3.42</v>
       </c>
       <c r="U4">
-        <v>1.3</v>
+        <v>1.26</v>
       </c>
       <c r="V4">
         <v>10</v>
@@ -985,40 +985,40 @@
         <v>1.05</v>
       </c>
       <c r="X4">
-        <v>1.04</v>
+        <v>1.12</v>
       </c>
       <c r="Y4">
-        <v>6</v>
+        <v>6.59</v>
       </c>
       <c r="Z4">
-        <v>1.43</v>
+        <v>1.47</v>
       </c>
       <c r="AA4">
         <v>2.4</v>
       </c>
       <c r="AB4">
-        <v>2.47</v>
+        <v>2.5</v>
       </c>
       <c r="AC4">
-        <v>1.5</v>
+        <v>1.52</v>
       </c>
       <c r="AD4">
         <v>5</v>
       </c>
       <c r="AE4">
-        <v>1.19</v>
+        <v>1.17</v>
       </c>
       <c r="AF4">
         <v>2.15</v>
       </c>
       <c r="AG4">
-        <v>1.6</v>
+        <v>1.7</v>
       </c>
       <c r="AH4">
-        <v>9.300000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AI4">
-        <v>1.05</v>
+        <v>1</v>
       </c>
       <c r="AJ4" t="s">
         <v>61</v>
@@ -1065,13 +1065,13 @@
         <v>60</v>
       </c>
       <c r="L5">
-        <v>1.92</v>
+        <v>1.82</v>
       </c>
       <c r="M5">
-        <v>3.7</v>
+        <v>4</v>
       </c>
       <c r="N5">
-        <v>3.25</v>
+        <v>3.33</v>
       </c>
       <c r="O5">
         <v>0</v>
@@ -1083,58 +1083,58 @@
         <v>0</v>
       </c>
       <c r="R5">
-        <v>1.3</v>
+        <v>1.24</v>
       </c>
       <c r="S5">
-        <v>3</v>
+        <v>3.8</v>
       </c>
       <c r="T5">
-        <v>2.4</v>
+        <v>2.1</v>
       </c>
       <c r="U5">
         <v>1.47</v>
       </c>
       <c r="V5">
-        <v>5.5</v>
+        <v>4.33</v>
       </c>
       <c r="W5">
-        <v>1.11</v>
+        <v>1.2</v>
       </c>
       <c r="X5">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y5">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="Z5">
-        <v>1.2</v>
+        <v>1.14</v>
       </c>
       <c r="AA5">
-        <v>3.8</v>
+        <v>4.45</v>
       </c>
       <c r="AB5">
-        <v>1.67</v>
+        <v>1.4</v>
       </c>
       <c r="AC5">
-        <v>2.2</v>
+        <v>2.55</v>
       </c>
       <c r="AD5">
-        <v>2.6</v>
+        <v>2.11</v>
       </c>
       <c r="AE5">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="AF5">
-        <v>1.55</v>
+        <v>1.47</v>
       </c>
       <c r="AG5">
-        <v>2.2</v>
+        <v>2.38</v>
       </c>
       <c r="AH5">
         <v>4.2</v>
       </c>
       <c r="AI5">
-        <v>1.16</v>
+        <v>1.29</v>
       </c>
       <c r="AJ5" t="s">
         <v>61</v>
@@ -1181,13 +1181,13 @@
         <v>60</v>
       </c>
       <c r="L6">
-        <v>2.28</v>
+        <v>2.77</v>
       </c>
       <c r="M6">
-        <v>2.81</v>
+        <v>2.82</v>
       </c>
       <c r="N6">
-        <v>3.1</v>
+        <v>3.25</v>
       </c>
       <c r="O6">
         <v>2</v>
@@ -1199,37 +1199,37 @@
         <v>2.25</v>
       </c>
       <c r="R6">
-        <v>1.57</v>
+        <v>1.53</v>
       </c>
       <c r="S6">
-        <v>2.25</v>
+        <v>2.14</v>
       </c>
       <c r="T6">
         <v>3.75</v>
       </c>
       <c r="U6">
-        <v>1.22</v>
+        <v>1.19</v>
       </c>
       <c r="V6">
         <v>12</v>
       </c>
       <c r="W6">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="X6">
-        <v>1.08</v>
+        <v>1.12</v>
       </c>
       <c r="Y6">
-        <v>7</v>
+        <v>5.45</v>
       </c>
       <c r="Z6">
-        <v>1.57</v>
+        <v>1.61</v>
       </c>
       <c r="AA6">
-        <v>2.4</v>
+        <v>2.26</v>
       </c>
       <c r="AB6">
-        <v>2.65</v>
+        <v>2.75</v>
       </c>
       <c r="AC6">
         <v>1.42</v>
@@ -1241,13 +1241,13 @@
         <v>1.13</v>
       </c>
       <c r="AF6">
-        <v>2.1</v>
+        <v>2.25</v>
       </c>
       <c r="AG6">
-        <v>1.62</v>
+        <v>1.52</v>
       </c>
       <c r="AH6">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AI6">
         <v>1</v>
@@ -1297,13 +1297,13 @@
         <v>60</v>
       </c>
       <c r="L7">
-        <v>1.81</v>
+        <v>1.83</v>
       </c>
       <c r="M7">
-        <v>3.82</v>
+        <v>3.9</v>
       </c>
       <c r="N7">
-        <v>3.6</v>
+        <v>3.15</v>
       </c>
       <c r="O7">
         <v>1.53</v>
@@ -1318,19 +1318,19 @@
         <v>1.22</v>
       </c>
       <c r="S7">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="T7">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="U7">
-        <v>1.6</v>
+        <v>1.65</v>
       </c>
       <c r="V7">
-        <v>4.75</v>
+        <v>4</v>
       </c>
       <c r="W7">
-        <v>1.15</v>
+        <v>1.2</v>
       </c>
       <c r="X7">
         <v>0</v>
@@ -1339,34 +1339,34 @@
         <v>0</v>
       </c>
       <c r="Z7">
-        <v>1.14</v>
+        <v>1.11</v>
       </c>
       <c r="AA7">
-        <v>4.5</v>
+        <v>5</v>
       </c>
       <c r="AB7">
-        <v>1.5</v>
+        <v>1.39</v>
       </c>
       <c r="AC7">
-        <v>2.44</v>
+        <v>2.7</v>
       </c>
       <c r="AD7">
-        <v>2.24</v>
+        <v>2</v>
       </c>
       <c r="AE7">
-        <v>1.56</v>
+        <v>1.65</v>
       </c>
       <c r="AF7">
-        <v>1.47</v>
+        <v>1.38</v>
       </c>
       <c r="AG7">
-        <v>2.4</v>
+        <v>2.8</v>
       </c>
       <c r="AH7">
-        <v>3.6</v>
+        <v>3.2</v>
       </c>
       <c r="AI7">
-        <v>1.22</v>
+        <v>1.26</v>
       </c>
       <c r="AJ7" t="s">
         <v>61</v>

--- a/jogos_2025-07-17.xlsx
+++ b/jogos_2025-07-17.xlsx
@@ -148,12 +148,12 @@
     <t>Iceland Úrvalsdeild</t>
   </si>
   <si>
+    <t>Brazil Serie B</t>
+  </si>
+  <si>
     <t>Brazil Serie A</t>
   </si>
   <si>
-    <t>Brazil Serie B</t>
-  </si>
-  <si>
     <t>USA MLS Next Pro</t>
   </si>
   <si>
@@ -163,12 +163,12 @@
     <t>Afturelding</t>
   </si>
   <si>
+    <t>Operário PR</t>
+  </si>
+  <si>
     <t>Fluminense</t>
   </si>
   <si>
-    <t>Operário PR</t>
-  </si>
-  <si>
     <t>Houston Dynamo FC II</t>
   </si>
   <si>
@@ -181,10 +181,10 @@
     <t>Fram</t>
   </si>
   <si>
+    <t>CRB</t>
+  </si>
+  <si>
     <t>Cruzeiro</t>
-  </si>
-  <si>
-    <t>CRB</t>
   </si>
   <si>
     <t>Whitecaps II</t>
@@ -717,13 +717,13 @@
         <v>60</v>
       </c>
       <c r="L2">
-        <v>2.46</v>
+        <v>2.4</v>
       </c>
       <c r="M2">
-        <v>3.52</v>
+        <v>3.5</v>
       </c>
       <c r="N2">
-        <v>2.44</v>
+        <v>2.48</v>
       </c>
       <c r="O2">
         <v>2.05</v>
@@ -735,52 +735,52 @@
         <v>1.8</v>
       </c>
       <c r="R2">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="S2">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="T2">
-        <v>2.43</v>
+        <v>2.38</v>
       </c>
       <c r="U2">
-        <v>1.48</v>
+        <v>1.52</v>
       </c>
       <c r="V2">
-        <v>5.75</v>
+        <v>5</v>
       </c>
       <c r="W2">
-        <v>1.13</v>
+        <v>1.09</v>
       </c>
       <c r="X2">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="Y2">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="Z2">
         <v>1.18</v>
       </c>
       <c r="AA2">
-        <v>4.35</v>
+        <v>4.4</v>
       </c>
       <c r="AB2">
-        <v>1.6</v>
+        <v>1.57</v>
       </c>
       <c r="AC2">
-        <v>2.1</v>
+        <v>2.25</v>
       </c>
       <c r="AD2">
-        <v>2.55</v>
+        <v>2.45</v>
       </c>
       <c r="AE2">
-        <v>1.48</v>
+        <v>1.5</v>
       </c>
       <c r="AF2">
         <v>1.55</v>
       </c>
       <c r="AG2">
-        <v>2.3</v>
+        <v>2.4</v>
       </c>
       <c r="AH2">
         <v>4.33</v>
@@ -833,76 +833,76 @@
         <v>60</v>
       </c>
       <c r="L3">
-        <v>2.25</v>
+        <v>2.05</v>
       </c>
       <c r="M3">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="N3">
-        <v>3.05</v>
+        <v>4.55</v>
       </c>
       <c r="O3">
-        <v>1.73</v>
+        <v>1.7</v>
       </c>
       <c r="P3">
-        <v>7.25</v>
+        <v>6.25</v>
       </c>
       <c r="Q3">
-        <v>2.5</v>
+        <v>2.88</v>
       </c>
       <c r="R3">
-        <v>1.62</v>
+        <v>1.56</v>
       </c>
       <c r="S3">
         <v>2.5</v>
       </c>
       <c r="T3">
-        <v>3.6</v>
+        <v>3.42</v>
       </c>
       <c r="U3">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="V3">
-        <v>7.5</v>
+        <v>10</v>
       </c>
       <c r="W3">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="X3">
         <v>1.12</v>
       </c>
       <c r="Y3">
-        <v>6.05</v>
+        <v>6.59</v>
       </c>
       <c r="Z3">
-        <v>1.57</v>
+        <v>1.47</v>
       </c>
       <c r="AA3">
-        <v>2.3</v>
+        <v>2.4</v>
       </c>
       <c r="AB3">
-        <v>2.87</v>
+        <v>2.5</v>
       </c>
       <c r="AC3">
-        <v>1.4</v>
+        <v>1.52</v>
       </c>
       <c r="AD3">
-        <v>5.25</v>
+        <v>5</v>
       </c>
       <c r="AE3">
-        <v>1.11</v>
+        <v>1.17</v>
       </c>
       <c r="AF3">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="AG3">
         <v>1.7</v>
       </c>
       <c r="AH3">
-        <v>11.5</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AI3">
-        <v>1.03</v>
+        <v>1</v>
       </c>
       <c r="AJ3" t="s">
         <v>61</v>
@@ -949,76 +949,76 @@
         <v>60</v>
       </c>
       <c r="L4">
-        <v>2.05</v>
+        <v>2.25</v>
       </c>
       <c r="M4">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="N4">
-        <v>4.55</v>
+        <v>3.05</v>
       </c>
       <c r="O4">
-        <v>1.7</v>
+        <v>1.73</v>
       </c>
       <c r="P4">
-        <v>6.25</v>
+        <v>7.25</v>
       </c>
       <c r="Q4">
-        <v>2.88</v>
+        <v>2.5</v>
       </c>
       <c r="R4">
-        <v>1.56</v>
+        <v>1.62</v>
       </c>
       <c r="S4">
         <v>2.5</v>
       </c>
       <c r="T4">
-        <v>3.42</v>
+        <v>3.6</v>
       </c>
       <c r="U4">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="V4">
-        <v>10</v>
+        <v>7.5</v>
       </c>
       <c r="W4">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="X4">
         <v>1.12</v>
       </c>
       <c r="Y4">
-        <v>6.59</v>
+        <v>6.05</v>
       </c>
       <c r="Z4">
-        <v>1.47</v>
+        <v>1.57</v>
       </c>
       <c r="AA4">
-        <v>2.4</v>
+        <v>2.3</v>
       </c>
       <c r="AB4">
-        <v>2.5</v>
+        <v>2.87</v>
       </c>
       <c r="AC4">
-        <v>1.52</v>
+        <v>1.4</v>
       </c>
       <c r="AD4">
-        <v>5</v>
+        <v>5.25</v>
       </c>
       <c r="AE4">
-        <v>1.17</v>
+        <v>1.11</v>
       </c>
       <c r="AF4">
-        <v>2.15</v>
+        <v>2.1</v>
       </c>
       <c r="AG4">
         <v>1.7</v>
       </c>
       <c r="AH4">
-        <v>9.199999999999999</v>
+        <v>11.5</v>
       </c>
       <c r="AI4">
-        <v>1</v>
+        <v>1.03</v>
       </c>
       <c r="AJ4" t="s">
         <v>61</v>
@@ -1154,7 +1154,7 @@
         <v>41</v>
       </c>
       <c r="C6" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D6" t="s">
         <v>47</v>
